--- a/docs/downloads/经营分_津河省区__唐山南片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_津河省区__唐山南片区_2026-10-18.xlsx
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -729,13 +729,13 @@
         <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
         <v>30</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
         <v>30</v>
@@ -771,17 +771,17 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>7439236383044012068</t>
+          <t>7406290618429507625</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>潮漫酒店（唐山新街万达广场店）</t>
+          <t>丽怡酒店（唐山曹妃甸工业区店）</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>潮漫酒店(唐山新街万达广场店)</t>
+          <t>丽怡酒店</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -793,7 +793,7 @@
         <v>82</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -852,24 +852,20 @@
           <t>唐山南片区</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>唐山市</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>6601149467607435268</t>
+          <t>7439236383044012068</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7天优品（唐山市小山人民医院店）</t>
+          <t>潮漫酒店（唐山新街万达广场店）</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7天优品酒店(唐山人民医院小山店)</t>
+          <t>潮漫酒店(唐山新街万达广场店)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -878,24 +874,24 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
         <v>30</v>
@@ -907,7 +903,7 @@
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
         <v>30</v>
@@ -940,20 +936,24 @@
           <t>唐山南片区</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>唐山市</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>7406290618429507625</t>
+          <t>6601149467607435268</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>丽怡酒店（唐山曹妃甸工业区店）</t>
+          <t>7天优品（唐山市小山人民医院店）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>丽怡酒店</t>
+          <t>7天优品酒店(唐山人民医院小山店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -962,36 +962,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N5" t="n">
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
         <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
         <v>30</v>
@@ -1031,22 +1031,22 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7302345968501032979</t>
+          <t>7232543592244316172</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>喆啡酒店（唐山海港龙泽国际店）</t>
+          <t>维也纳酒店（5.0唐山滦南建设路店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>喆啡酒店(唐山海港龙泽国际店)</t>
+          <t>维也纳酒店(5.0唐山滦南建设路店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1119,22 +1119,22 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7232543592244316172</t>
+          <t>6601172037241161732</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0唐山滦南建设路店）</t>
+          <t>麗枫酒店·唐山火车站店</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0唐山滦南建设路店)</t>
+          <t>丽枫酒店(唐山火车站店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1207,29 +1207,29 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6601172037241161732</t>
+          <t>7310824642271250470</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>麗枫酒店·唐山火车站店</t>
+          <t>麗枫酒店唐山乐亭京唐港店</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>丽枫酒店(唐山火车站店)</t>
+          <t>麗枫酒店(唐山乐亭京唐港店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>87</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1249,13 +1249,13 @@
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1295,29 +1295,29 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7310824642271250470</t>
+          <t>6713650905083840516</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>麗枫酒店唐山乐亭京唐港店</t>
+          <t>麗枫酒店（唐山师范学院会展中心店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>麗枫酒店(唐山乐亭京唐港店)</t>
+          <t>麗枫酒店(唐山师范学院会展中心店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>87</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1337,13 +1337,13 @@
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1383,17 +1383,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6713650905083840516</t>
+          <t>7302345968501032979</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>麗枫酒店（唐山师范学院会展中心店）</t>
+          <t>喆啡酒店（唐山海港龙泽国际店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>麗枫酒店(唐山师范学院会展中心店)</t>
+          <t>喆啡酒店(唐山海港龙泽国际店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
@@ -1995,17 +1995,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7280417745231939596</t>
+          <t>7317832777913600036</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>维也纳国际（5.0版唐山海港文化大街店）</t>
+          <t>麗枫酒店唐山曹妃甸工业区店</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>维也纳国际(唐山海港文化大街店)</t>
+          <t>丽枫酒店(唐山曹妃甸工业区店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2014,36 +2014,36 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>搭门店,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2083,17 +2083,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7405478165960722495</t>
+          <t>7280417745231939596</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>锦江之星（滦南县北河公园酒店）</t>
+          <t>维也纳国际（5.0版唐山海港文化大街店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>锦江之星酒店(滦南县北河公园店)</t>
+          <t>维也纳国际(唐山海港文化大街店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>搭门店,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2119,19 +2119,19 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2171,55 +2171,55 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7234809474035222568</t>
+          <t>7405478165960722495</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>喆啡酒店唐山滦南县建设路店</t>
+          <t>锦江之星（滦南县北河公园酒店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>喆啡酒店(唐山滦南县建设路店)</t>
+          <t>锦江之星酒店(滦南县北河公园店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2259,33 +2259,33 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7317832777913600036</t>
+          <t>7234809474035222568</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>麗枫酒店唐山曹妃甸工业区店</t>
+          <t>喆啡酒店唐山滦南县建设路店</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>丽枫酒店(唐山曹妃甸工业区店)</t>
+          <t>喆啡酒店(唐山滦南县建设路店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2295,19 +2295,19 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
